--- a/artfynd/A 30722-2023 artfynd.xlsx
+++ b/artfynd/A 30722-2023 artfynd.xlsx
@@ -714,11 +714,7 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
